--- a/artfynd/A 54703-2024 artfynd.xlsx
+++ b/artfynd/A 54703-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69018379</v>
+        <v>69018378</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685994.1982564983</v>
+        <v>686164</v>
       </c>
       <c r="R2" t="n">
-        <v>6603080.263280223</v>
+        <v>6603038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69018451</v>
+        <v>69018379</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,43 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Österåker, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685689.1141198672</v>
+        <v>685994</v>
       </c>
       <c r="R3" t="n">
-        <v>6602661.140304567</v>
+        <v>6603080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +844,9 @@
           <t>2016-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,50 +877,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69018380</v>
+        <v>69018451</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Österåker, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686234.2337596716</v>
+        <v>685689</v>
       </c>
       <c r="R4" t="n">
-        <v>6602766.902220027</v>
+        <v>6602661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,19 +954,9 @@
           <t>2016-06-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-06-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,50 +987,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69018381</v>
+        <v>69017793</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Österåker, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686249.7918627718</v>
+        <v>685798</v>
       </c>
       <c r="R5" t="n">
-        <v>6602802.233257083</v>
+        <v>6602820</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,19 +1064,9 @@
           <t>2016-06-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-06-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,6 +1090,208 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69018380</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Österåker, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>686234</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6602767</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-06-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-06-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson, Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>69018381</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Österåker, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>686250</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6602802</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-06-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-06-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson, Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 54703-2024 artfynd.xlsx
+++ b/artfynd/A 54703-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69018378</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69018379</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69018380</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69018381</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69018451</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,8 +1326,21 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69017793</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>